--- a/codespace/results/ch4_fw2_stratified_residual_summary.xlsx
+++ b/codespace/results/ch4_fw2_stratified_residual_summary.xlsx
@@ -472,16 +472,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>12561</v>
+        <v>15051</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02941808794502665</v>
+        <v>0.01383916276213659</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0413945494299377</v>
+        <v>0.01940454949869756</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6456958249650306</v>
+        <v>0.3298230643562644</v>
       </c>
     </row>
     <row r="3">
@@ -496,16 +496,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>318</v>
+        <v>348</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03067051106522531</v>
+        <v>0.0107919334728442</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02888434144527188</v>
+        <v>0.01397126575889248</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1652203765740071</v>
+        <v>0.07426285774873864</v>
       </c>
     </row>
     <row r="4">
@@ -523,13 +523,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0003629937733874988</v>
+        <v>0.01016841966176707</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0003629937733874988</v>
+        <v>0.01016841966176707</v>
       </c>
     </row>
     <row r="5">
@@ -544,16 +544,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>12720</v>
+        <v>12880</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02764556760878042</v>
+        <v>0.017296168663385</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04025673047358561</v>
+        <v>0.02508988093623821</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5074494661146037</v>
+        <v>0.329899745166546</v>
       </c>
     </row>
     <row r="6">
@@ -568,16 +568,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03079261660373901</v>
+        <v>0.01680336721739534</v>
       </c>
       <c r="E6" t="n">
-        <v>0.05088228782728171</v>
+        <v>0.02076478427205521</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2990253784148339</v>
+        <v>0.1715814622034434</v>
       </c>
     </row>
     <row r="7">
@@ -595,13 +595,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03780298458998577</v>
+        <v>0.0217053515517317</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03780298458998577</v>
+        <v>0.0217053515517317</v>
       </c>
     </row>
   </sheetData>
